--- a/test_new.xlsx
+++ b/test_new.xlsx
@@ -446,41 +446,136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:AP18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr"/>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dust3r</t>
+          <t>abs_diff</t>
         </is>
       </c>
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dust3r_abs</t>
+          <t>abs_metric</t>
         </is>
       </c>
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dust3r_abs_trim</t>
+          <t>abs_trim</t>
         </is>
       </c>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>abs_trim_diff</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>abs_trim_splitmix</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>abs_trim_splitmix_diff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>diff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dust3r</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dust3r_abs</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dust3r_abs_diff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="n"/>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dust3r_abs_trim</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="n"/>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dust3r_abs_trim_diff</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="n"/>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>dust3r_abs_trim_splitmix</t>
         </is>
       </c>
-      <c r="K1" s="1" t="n"/>
+      <c r="AC1" s="1" t="n"/>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dust3r_abs_trim_splitmix_diff</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="n"/>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dust3r_abs_trim_splitmix_mvs_filter</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="n"/>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dust3r_abs_trim_splitmix_mvs_filter_diff</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dust3r_diff</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="n"/>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>origin</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="n"/>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>trim</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="n"/>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>trim_diff</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr"/>
@@ -534,6 +629,161 @@
           <t>overall</t>
         </is>
       </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="Z2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="AB2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="AC2" s="1" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="AD2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="AE2" s="1" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="AF2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="AG2" s="1" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="AH2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="AI2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="AJ2" s="1" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="AK2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="AL2" s="1" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="AM2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="AN2" s="1" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="AO2" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="AP2" s="1" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -545,39 +795,164 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>0.7288571285928753</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7634262829980014</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7647317435079207</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7243844429393105</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.7644950254998472</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.7279856752817102</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0.7647484110889782</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.765518213103956</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0.8031730211219013</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>0.8077939370188795</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>0.8929815423340306</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.8032249816055246</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.8843296627500647</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.7721553959165697</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.843649265187724</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.7828622502144714</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.8982256220368359</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>dtu24</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
         <v>0.7298868765342065</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>dtu24</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>0.8031730211219013</v>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="AN4" t="n">
+        <v>0.7118316673540239</v>
+      </c>
+      <c r="AO4" t="inlineStr">
         <is>
           <t>dtu24</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>0.8077939370188795</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>dtu24</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8032249816055246</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dtu24</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0.7721553959165697</v>
+      <c r="AP4" t="n">
+        <v>0.753585769541907</v>
       </c>
     </row>
     <row r="5">
@@ -590,39 +965,162 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>2.105568346029909</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2.04684986515101</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.050664848926569</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2.012983754288633</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1.780494107164647</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1.734785731702275</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.999155680528524</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>3.074794512556779</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>3.124967838730573</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>3.305458503987913</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.054960836187163</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.263987362512466</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.038704759655974</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.106092329987496</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.57085372456102</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>3.320448982586859</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>dtu37</t>
+        </is>
+      </c>
+      <c r="AL5" t="n">
         <v>2.186356227091961</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>dtu37</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>3.074794512556779</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="AN5" t="n">
+        <v>2.07777448881906</v>
+      </c>
+      <c r="AO5" t="inlineStr">
         <is>
           <t>dtu37</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>3.124967838730573</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>dtu37</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.054960836187163</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dtu37</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>3.038704759655974</v>
+      <c r="AP5" t="n">
+        <v>2.184549385112569</v>
       </c>
     </row>
     <row r="6">
@@ -635,7 +1133,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.832347287361026</v>
+        <v>1.795446980254803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -643,31 +1141,156 @@
         </is>
       </c>
       <c r="E6" t="n">
+        <v>1.246007357080495</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1.254082985346741</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.860335824453365</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1.209601701766425</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1.806773845645604</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>1.218912251307703</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.205373707268623</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
         <v>1.161657410822745</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>dtu40</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="U6" t="n">
         <v>1.142669952931181</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>dtu40</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="W6" t="n">
+        <v>1.199687275263325</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
         <v>1.245604801895575</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>dtu40</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="AA6" t="n">
+        <v>1.256827562424339</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
         <v>1.170955118134007</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.184116182324041</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.2618249015112</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.164453993007511</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.866459283061187</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.795735293964126</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>dtu40</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.13661077050188</v>
       </c>
     </row>
     <row r="7">
@@ -680,39 +1303,164 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>0.8119782827229516</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7964266550843675</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7997214068308848</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8044735290491787</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.7918260036431075</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0.7982728101329193</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0.7860505791002531</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.8940817323982289</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.8079547674119257</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>0.8056425301219159</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>0.8198818292281829</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.8006369224196929</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.8117786589713547</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.7933361637011991</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.7959145134442938</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8332756140730994</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.8109112672509241</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>dtu55</t>
+        </is>
+      </c>
+      <c r="AL7" t="n">
         <v>0.8067212995968978</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>dtu55</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0.8079547674119257</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="AN7" t="n">
+        <v>0.8078830509444543</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>dtu55</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0.8056425301219159</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>dtu55</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.8006369224196929</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dtu55</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0.7933361637011991</v>
+      <c r="AP7" t="n">
+        <v>0.7947382143123743</v>
       </c>
     </row>
     <row r="8">
@@ -725,39 +1473,164 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>1.267098486175165</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1.223965218680921</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1.092085170243713</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.391531678410959</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1.259296503848994</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1.142611011794201</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0.9864649868182547</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.160356928690529</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>1.073602346717634</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>1.026016008341941</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>1.087773494884454</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.095362228419358</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.095919774006538</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.043310443782703</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.056459579246888</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.262045760660945</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.053271165846866</v>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>dtu63</t>
+        </is>
+      </c>
+      <c r="AL8" t="n">
         <v>1.233239341392728</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>dtu63</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>1.073602346717634</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="AN8" t="n">
+        <v>1.247467087404241</v>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>dtu63</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>1.026016008341941</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>dtu63</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.095362228419358</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dtu63</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>1.043310443782703</v>
+      <c r="AP8" t="n">
+        <v>1.163448368548926</v>
       </c>
     </row>
     <row r="9">
@@ -770,39 +1643,164 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>1.337980911365232</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1.256061741596737</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1.405170675670976</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.381391313587815</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1.264015263147815</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1.400878726114162</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>1.35965746301024</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.242158658515039</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>1.360828223678936</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>1.356024724787942</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>1.379829299631632</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.364543206854926</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.384798204518263</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.334081010235268</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.366802956755715</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.348887044440441</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.386039530621844</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>dtu65</t>
+        </is>
+      </c>
+      <c r="AL9" t="n">
         <v>1.326098964396741</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>dtu65</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>1.360828223678936</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="AN9" t="n">
+        <v>1.344912965872275</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>dtu65</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>1.356024724787942</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>dtu65</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.364543206854926</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dtu65</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>1.334081010235268</v>
+      <c r="AP9" t="n">
+        <v>1.224548039942664</v>
       </c>
     </row>
     <row r="10">
@@ -815,39 +1813,164 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>0.6522993161981528</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.6437872569724941</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.667743766021597</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.6507003626941229</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.6447260233137236</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0.6514396087274961</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0.6449602795997411</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.6404468192826047</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6686430005254028</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>0.6730025192427487</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>0.6897300715809815</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.6650862929195324</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.6809285723321304</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.6513406543030277</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.6641110578309384</v>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.6596157045587577</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.6912828802312465</v>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>dtu69</t>
+        </is>
+      </c>
+      <c r="AL10" t="n">
         <v>0.6502249843131619</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>dtu69</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>0.6686430005254028</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="AN10" t="n">
+        <v>0.6466330767201273</v>
+      </c>
+      <c r="AO10" t="inlineStr">
         <is>
           <t>dtu69</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0.6730025192427487</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>dtu69</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.6650862929195324</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dtu69</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>0.6513406543030277</v>
+      <c r="AP10" t="n">
+        <v>0.6430031007863088</v>
       </c>
     </row>
     <row r="11">
@@ -860,39 +1983,164 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1.162158982066199</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1.161324579240755</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1.164000153345239</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.115342148208979</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1.170212175974097</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1.164550282866387</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>1.14436217345633</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.159872297077577</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>1.674321656446061</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>1.730802339009224</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>1.655069759724978</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.747637095830143</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.602577179165499</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.150719517101571</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.181067887483006</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.183971725550028</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.745301180900346</v>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>dtu83</t>
+        </is>
+      </c>
+      <c r="AL11" t="n">
         <v>1.141242589022657</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>dtu83</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>1.674321656446061</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="AN11" t="n">
+        <v>1.160680042718037</v>
+      </c>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>dtu83</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>1.730802339009224</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>dtu83</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.747637095830143</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dtu83</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>1.150719517101571</v>
+      <c r="AP11" t="n">
+        <v>1.16485765668447</v>
       </c>
     </row>
     <row r="12">
@@ -905,39 +2153,164 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>1.258066177511103</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1.271497727464544</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1.216385012909739</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.277092699457505</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1.272954837862073</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1.244290554521436</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>1.240132861828528</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.254074448487894</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>1.291967093035484</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>1.290938588885358</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>1.305333973928107</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.270704822101109</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.305844601982469</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.24670048311212</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.248482231281943</v>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.251777549997469</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.306984178317181</v>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>dtu97</t>
+        </is>
+      </c>
+      <c r="AL12" t="n">
         <v>1.237915588525997</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>dtu97</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>1.291967093035484</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="AN12" t="n">
+        <v>1.237233501310391</v>
+      </c>
+      <c r="AO12" t="inlineStr">
         <is>
           <t>dtu97</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>1.290938588885358</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>dtu97</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.270704822101109</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dtu97</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>1.24670048311212</v>
+      <c r="AP12" t="n">
+        <v>1.246506847712654</v>
       </c>
     </row>
     <row r="13">
@@ -950,39 +2323,164 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>0.7557550777068758</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6588681302277402</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.723742135406978</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7693441594134489</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.6707668147185956</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0.781268633891027</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0.7134896649736652</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.6757298382939967</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>0.8177385307933929</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>0.8171367956267545</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>0.8415492809503502</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.817362525364928</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.8440624344531734</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.8242835988061926</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.8194284915938532</v>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.8404301597900579</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.8590097595331607</v>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>dtu105</t>
+        </is>
+      </c>
+      <c r="AL13" t="n">
         <v>0.7600464184249996</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="AM13" t="inlineStr">
         <is>
           <t>dtu105</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>0.8177385307933929</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="AN13" t="n">
+        <v>0.7641754538014718</v>
+      </c>
+      <c r="AO13" t="inlineStr">
         <is>
           <t>dtu105</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0.8171367956267545</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>dtu105</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.817362525364928</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dtu105</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>0.8242835988061926</v>
+      <c r="AP13" t="n">
+        <v>0.6761589997451261</v>
       </c>
     </row>
     <row r="14">
@@ -995,39 +2493,164 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>0.8514209848983532</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7817420802183691</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7799227310491292</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7913075426849916</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0.7923437362651856</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0.7811538023229527</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0.7868800707690801</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.7816430117852854</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>0.9696295769875822</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>0.9359755213981475</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02860622852176</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.9005096255806424</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.948174015053708</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.7894334172610914</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.8553918273603295</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.7279835579517023</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.046528131381059</v>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>dtu106</t>
+        </is>
+      </c>
+      <c r="AL14" t="n">
         <v>0.8218005474560828</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="AM14" t="inlineStr">
         <is>
           <t>dtu106</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>0.9696295769875822</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="AN14" t="n">
+        <v>0.8260545865322949</v>
+      </c>
+      <c r="AO14" t="inlineStr">
         <is>
           <t>dtu106</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>0.9359755213981475</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>dtu106</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.9005096255806424</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>dtu106</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>0.7894334172610914</v>
+      <c r="AP14" t="n">
+        <v>0.8141446164063832</v>
       </c>
     </row>
     <row r="15">
@@ -1040,39 +2663,164 @@
         </is>
       </c>
       <c r="C15" t="n">
+        <v>0.4949971852611444</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.5111248546103062</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.5401080677195591</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.493989051443398</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0.5122626750533077</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0.4815385453205167</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0.4867354819730215</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.5263867585603683</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>0.4793585302008293</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>0.5219784555188478</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>0.5327652978130448</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5203307528994665</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.4852914609842244</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.5238071300212714</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.5202907025334849</v>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.4872987072225866</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.4952082032139224</v>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>dtu110</t>
+        </is>
+      </c>
+      <c r="AL15" t="n">
         <v>0.4952321917013248</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="AM15" t="inlineStr">
         <is>
           <t>dtu110</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>0.4793585302008293</v>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="AN15" t="n">
+        <v>0.4917738662556714</v>
+      </c>
+      <c r="AO15" t="inlineStr">
         <is>
           <t>dtu110</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0.5219784555188478</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>dtu110</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0.5203307528994665</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>dtu110</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>0.5238071300212714</v>
+      <c r="AP15" t="n">
+        <v>0.493842687952352</v>
       </c>
     </row>
     <row r="16">
@@ -1085,39 +2833,164 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>0.4165056669452371</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.4213847384424834</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.4192469363093754</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4256710588295262</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0.4402602974012537</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0.4101945271243571</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0.4089821237121412</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.4441698508765211</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4060224126010153</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>0.4056659710338726</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>0.4059275728924355</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4069430965240721</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.4057965673199535</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.4064015307143303</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.4047551813207528</v>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.4073637500070079</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.4064199055049986</v>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>dtu114</t>
+        </is>
+      </c>
+      <c r="AL16" t="n">
         <v>0.4181819812287486</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="AM16" t="inlineStr">
         <is>
           <t>dtu114</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>0.4060224126010153</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="AN16" t="n">
+        <v>0.4090854641363367</v>
+      </c>
+      <c r="AO16" t="inlineStr">
         <is>
           <t>dtu114</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0.4056659710338726</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>dtu114</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>0.4069430965240721</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>dtu114</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>0.4064015307143303</v>
+      <c r="AP16" t="n">
+        <v>0.4462031872412486</v>
       </c>
     </row>
     <row r="17">
@@ -1130,39 +3003,164 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>0.8672267203237629</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8715723170765758</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1.530319420136388</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8414319305698247</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0.8769810479158993</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0.7564474611497365</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0.7739908101052921</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.8797293052353001</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="S17" t="n">
+        <v>1.597948709191599</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>1.666197350600944</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>1.648063203904647</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.509972278250586</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.589329512504629</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.512269161288619</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.580478192370717</v>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.7669745199441691</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.626933882500236</v>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>dtu118</t>
+        </is>
+      </c>
+      <c r="AL17" t="n">
         <v>0.8475157094078333</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="AM17" t="inlineStr">
         <is>
           <t>dtu118</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>1.597948709191599</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="AN17" t="n">
+        <v>0.8491182732521311</v>
+      </c>
+      <c r="AO17" t="inlineStr">
         <is>
           <t>dtu118</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>1.666197350600944</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>dtu118</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.509972278250586</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>dtu118</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>1.512269161288619</v>
+      <c r="AP17" t="n">
+        <v>0.8750729380817086</v>
       </c>
     </row>
     <row r="18">
@@ -1175,48 +3173,188 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>1.021255000556852</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1.031709465749275</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9801495974482817</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.037647833651282</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1.067255730409917</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0.9491991330821276</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0.9486820773043685</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.04677196920434</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="S18" t="n">
+        <v>0.9856182541606628</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>0.9780673091022998</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>0.9794391215483682</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.9709583009925474</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.9758232070148531</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.9512412624704789</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.9570159432216826</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.954784929716862</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.96557454666441</v>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>dtu122</t>
+        </is>
+      </c>
+      <c r="AL18" t="n">
         <v>1.067285029896799</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="AM18" t="inlineStr">
         <is>
           <t>dtu122</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>0.9856182541606628</v>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="AN18" t="n">
+        <v>1.055713984463366</v>
+      </c>
+      <c r="AO18" t="inlineStr">
         <is>
           <t>dtu122</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>0.9780673091022998</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>dtu122</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0.9709583009925474</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>dtu122</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>0.9512412624704789</v>
+      <c r="AP18" t="n">
+        <v>1.092139483818474</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="20">
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="H1:I1"/>
+    <mergeCell ref="AI1:AJ1"/>
     <mergeCell ref="J1:K1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="V1:W1"/>
     <mergeCell ref="B1:C1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
